--- a/outputs/excel/CodeCritters_TB_Comparison_Report.xlsx
+++ b/outputs/excel/CodeCritters_TB_Comparison_Report.xlsx
@@ -495,7 +495,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PythonMuse LLC | Article 33: Two Trial Balances Walk Into a Spreadsheet</t>
+          <t>PythonMuse LLC | Training &amp; Demo Template</t>
         </is>
       </c>
     </row>
